--- a/Experiments/outputs/scenario_1_np.xlsx
+++ b/Experiments/outputs/scenario_1_np.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>141.7610776860337</v>
+        <v>118.3652961962367</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02832794189453125</v>
+        <v>0.0688478946685791</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>248.7284536078492</v>
+        <v>249.586872435253</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09351205825805664</v>
+        <v>0.2986409664154053</v>
       </c>
       <c r="J2" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="M2" t="n">
-        <v>695.9628247054528</v>
+        <v>769.3882646426875</v>
       </c>
       <c r="N2" t="n">
-        <v>1.430883169174194</v>
+        <v>1.439969778060913</v>
       </c>
       <c r="O2" t="n">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>704</v>
+        <v>666</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7963094110004652</v>
+        <v>0.8461566134606864</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6426124431098506</v>
+        <v>0.6756034840859394</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>92.21564891392875</v>
+        <v>105.0961169900146</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02605414390563965</v>
+        <v>0.05943083763122559</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>215.2307734558846</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1209769248962402</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>42</v>
+      </c>
+      <c r="M3" t="n">
+        <v>753.6455349937642</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.652130126953125</v>
+      </c>
+      <c r="O3" t="n">
+        <v>253</v>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>222.7565722642206</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.08521318435668945</v>
-      </c>
-      <c r="J3" t="n">
-        <v>50</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>54</v>
-      </c>
-      <c r="M3" t="n">
-        <v>733.2012732644147</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.322788238525391</v>
-      </c>
-      <c r="O3" t="n">
-        <v>234</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
       <c r="Q3" t="n">
-        <v>695</v>
+        <v>736</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8742287387154155</v>
+        <v>0.8605496720804109</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6961863264742481</v>
+        <v>0.7144137880977885</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>69.74797305235015</v>
+        <v>81.16354231513206</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03549098968505859</v>
+        <v>0.06696796417236328</v>
       </c>
       <c r="E4" t="n">
+        <v>38</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>193.42104039522</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2683999538421631</v>
+      </c>
+      <c r="J4" t="n">
+        <v>44</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" t="n">
         <v>47</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>200.3798710541816</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.09443521499633789</v>
-      </c>
-      <c r="J4" t="n">
-        <v>46</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>50</v>
-      </c>
       <c r="M4" t="n">
-        <v>715.6470170762082</v>
+        <v>752.7696181489061</v>
       </c>
       <c r="N4" t="n">
-        <v>1.603490114212036</v>
+        <v>2.017203092575073</v>
       </c>
       <c r="O4" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>674</v>
+        <v>709</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9025385820270626</v>
+        <v>0.8921801035026934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7200018077727228</v>
+        <v>0.7430541353796252</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>143.1481353946453</v>
+        <v>95.83621859726306</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03827214241027832</v>
+        <v>0.05959701538085938</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>232.0119263385892</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1781899929046631</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38</v>
+      </c>
+      <c r="K5" t="n">
         <v>8</v>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>224.9235945507858</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.1339449882507324</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>49</v>
       </c>
-      <c r="K5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>54</v>
-      </c>
       <c r="M5" t="n">
-        <v>738.5713650973842</v>
+        <v>748.5054143474919</v>
       </c>
       <c r="N5" t="n">
-        <v>1.648717164993286</v>
+        <v>2.459843873977661</v>
       </c>
       <c r="O5" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>659</v>
+        <v>708</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8061823918995689</v>
+        <v>0.8719632259697038</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6954612578012302</v>
+        <v>0.6900330687108721</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>159.5609725848301</v>
+        <v>131.1954572843518</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02433204650878906</v>
+        <v>0.08835625648498535</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>235.5252761492508</v>
+        <v>203.5315558113108</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09837007522583008</v>
+        <v>0.2088720798492432</v>
       </c>
       <c r="J6" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K6" t="n">
         <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M6" t="n">
-        <v>698.290560187336</v>
+        <v>735.3129361597635</v>
       </c>
       <c r="N6" t="n">
-        <v>1.475016832351685</v>
+        <v>1.78220009803772</v>
       </c>
       <c r="O6" t="n">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>594</v>
+        <v>719</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7714977379301484</v>
+        <v>0.8215787444601047</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6627116424342546</v>
+        <v>0.723204168181411</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>95.85692869353532</v>
+        <v>93.63426036486405</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03287291526794434</v>
+        <v>0.06856393814086914</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>280.1848580236523</v>
+        <v>245.3868304774538</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09248614311218262</v>
+        <v>0.2893989086151123</v>
       </c>
       <c r="J7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K7" t="n">
         <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>754.0245893556222</v>
+        <v>732.9675500910408</v>
       </c>
       <c r="N7" t="n">
-        <v>1.525273084640503</v>
+        <v>2.020387887954712</v>
       </c>
       <c r="O7" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8728729406882431</v>
+        <v>0.8722531981760531</v>
       </c>
       <c r="S7" t="n">
-        <v>0.628414163173254</v>
+        <v>0.6652146054119658</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>79.13359487157322</v>
+        <v>90.24715950406051</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05068492889404297</v>
+        <v>0.05666804313659668</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>197.1751270567069</v>
+        <v>269.7540848196751</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1240448951721191</v>
+        <v>0.2566771507263184</v>
       </c>
       <c r="J8" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="M8" t="n">
-        <v>691.7540879795997</v>
+        <v>724.6349986869617</v>
       </c>
       <c r="N8" t="n">
-        <v>1.9775230884552</v>
+        <v>1.512310981750488</v>
       </c>
       <c r="O8" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8856044420312744</v>
+        <v>0.8754584588550259</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7149635535474831</v>
+        <v>0.6277379849048563</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>118.1865568312856</v>
+        <v>125.7871432229609</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04708194732666016</v>
+        <v>0.04133081436157227</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>240.3428281815548</v>
+        <v>271.7328794000417</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1304750442504883</v>
+        <v>0.2068979740142822</v>
       </c>
       <c r="J9" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="M9" t="n">
-        <v>771.4962097731318</v>
+        <v>765.4354777467846</v>
       </c>
       <c r="N9" t="n">
-        <v>2.036991119384766</v>
+        <v>1.297139883041382</v>
       </c>
       <c r="O9" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>627</v>
+        <v>658</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8468086358246144</v>
+        <v>0.8356659093027137</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6884717965727524</v>
+        <v>0.6449957085867736</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>112.9429588985206</v>
+        <v>129.703685781323</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0397648811340332</v>
+        <v>0.04630804061889648</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>237.7220864484091</v>
+        <v>213.9981127568157</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1550848484039307</v>
+        <v>0.1639218330383301</v>
       </c>
       <c r="J10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="M10" t="n">
-        <v>724.2037338456036</v>
+        <v>754.8528246475803</v>
       </c>
       <c r="N10" t="n">
-        <v>1.965098142623901</v>
+        <v>1.341639041900635</v>
       </c>
       <c r="O10" t="n">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>631</v>
+        <v>694</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8440453236842888</v>
+        <v>0.8281735438403135</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6717469472491145</v>
+        <v>0.7165035278807821</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>121.7383968260562</v>
+        <v>94.62498062662753</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04261493682861328</v>
+        <v>0.04427814483642578</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>200.6156373373478</v>
+        <v>186.4108110563739</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1159360408782959</v>
+        <v>0.1189761161804199</v>
       </c>
       <c r="J11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M11" t="n">
-        <v>725.9927992522092</v>
+        <v>721.7006170604338</v>
       </c>
       <c r="N11" t="n">
-        <v>1.334936141967773</v>
+        <v>1.586863279342651</v>
       </c>
       <c r="O11" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8323145946468756</v>
+        <v>0.8688861026445487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7236671802475357</v>
+        <v>0.7417061775343277</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>114.4380213192057</v>
+        <v>101.4405207157278</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02627921104431152</v>
+        <v>0.08457088470458984</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
         <v>6</v>
       </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
       <c r="H12" t="n">
-        <v>237.5759696503887</v>
+        <v>226.7696521977685</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07141304016113281</v>
+        <v>0.187614917755127</v>
       </c>
       <c r="J12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M12" t="n">
-        <v>707.9165137621403</v>
+        <v>733.5651612788949</v>
       </c>
       <c r="N12" t="n">
-        <v>1.200607061386108</v>
+        <v>1.605535984039307</v>
       </c>
       <c r="O12" t="n">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>599</v>
+        <v>729</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8383453146035001</v>
+        <v>0.8617157328752135</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6644011475480085</v>
+        <v>0.6908663822005682</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>118.49696530469</v>
+        <v>107.5665437837308</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02532720565795898</v>
+        <v>0.05737400054931641</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13" t="n">
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>200.2737859334157</v>
+        <v>207.9528149049131</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07608866691589355</v>
+        <v>0.1528868675231934</v>
       </c>
       <c r="J13" t="n">
         <v>42</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>745.9268459678965</v>
+        <v>721.5972737966805</v>
       </c>
       <c r="N13" t="n">
-        <v>1.399592876434326</v>
+        <v>1.425030946731567</v>
       </c>
       <c r="O13" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8411413050150632</v>
+        <v>0.8509327187202775</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7315101514096262</v>
+        <v>0.7118159637566667</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>93.44257567579622</v>
+        <v>141.5911720852621</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02963900566101074</v>
+        <v>0.04549098014831543</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>185.305607383553</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1484138965606689</v>
+      </c>
+      <c r="J14" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" t="n">
         <v>5</v>
       </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>241.7622778618507</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.1068689823150635</v>
-      </c>
-      <c r="J14" t="n">
-        <v>46</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7</v>
-      </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>710.0963785238928</v>
+        <v>741.9063554823992</v>
       </c>
       <c r="N14" t="n">
-        <v>1.364038944244385</v>
+        <v>1.367412090301514</v>
       </c>
       <c r="O14" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8684086012802386</v>
+        <v>0.8091522318969794</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6595359655763741</v>
+        <v>0.7502304623565809</v>
       </c>
     </row>
     <row r="15">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>122.5673880619794</v>
+        <v>114.8183526218982</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0256798267364502</v>
+        <v>0.04624819755554199</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
@@ -1338,40 +1338,40 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>215.6890778921485</v>
+        <v>229.0163551927602</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08326005935668945</v>
+        <v>0.1824760437011719</v>
       </c>
       <c r="J15" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="M15" t="n">
-        <v>720.2427813014185</v>
+        <v>736.4800533527798</v>
       </c>
       <c r="N15" t="n">
-        <v>1.383632898330688</v>
+        <v>1.198349237442017</v>
       </c>
       <c r="O15" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>639</v>
+        <v>683</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8298248989868244</v>
+        <v>0.8440984897022061</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7005328154731153</v>
+        <v>0.689039296923009</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>113.6034233203707</v>
+        <v>114.2003615023111</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02751708030700684</v>
+        <v>0.06607413291931152</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>237.8577908841935</v>
+        <v>300.738406665151</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07992696762084961</v>
+        <v>0.3562676906585693</v>
       </c>
       <c r="J16" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>731.8783687212438</v>
+        <v>739.3868427635132</v>
       </c>
       <c r="N16" t="n">
-        <v>1.147645235061646</v>
+        <v>1.485006093978882</v>
       </c>
       <c r="O16" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>623</v>
+        <v>706</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8447782744025331</v>
+        <v>0.8455472089880869</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6750036603762662</v>
+        <v>0.5932597264767129</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>103.2338159159939</v>
+        <v>106.3928629078088</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03072404861450195</v>
+        <v>0.04628801345825195</v>
       </c>
       <c r="E17" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>218.1546004347765</v>
+        <v>198.5210909402427</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07769489288330078</v>
+        <v>0.1445193290710449</v>
       </c>
       <c r="J17" t="n">
         <v>39</v>
       </c>
       <c r="K17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L17" t="n">
         <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>741.3947202990237</v>
+        <v>703.4495007409195</v>
       </c>
       <c r="N17" t="n">
-        <v>1.237929105758667</v>
+        <v>1.503304958343506</v>
       </c>
       <c r="O17" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>614</v>
+        <v>679</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8607572820664854</v>
+        <v>0.84875550725994</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7057510736699216</v>
+        <v>0.7177891366314892</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>115.8147227444545</v>
+        <v>90.74072970109657</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02545833587646484</v>
+        <v>0.03913593292236328</v>
       </c>
       <c r="E18" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>214.1780465207259</v>
+        <v>247.9286376573599</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08111786842346191</v>
+        <v>0.1899361610412598</v>
       </c>
       <c r="J18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="M18" t="n">
-        <v>729.2083112636758</v>
+        <v>733.9165010858038</v>
       </c>
       <c r="N18" t="n">
-        <v>1.237452745437622</v>
+        <v>1.392441272735596</v>
       </c>
       <c r="O18" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>626</v>
+        <v>675</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8411774510033295</v>
+        <v>0.8763609626342386</v>
       </c>
       <c r="S18" t="n">
-        <v>0.706286882345639</v>
+        <v>0.662184134992798</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>91.31904425697222</v>
+        <v>127.9452338167034</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0306241512298584</v>
+        <v>0.04881405830383301</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>237.0625647192433</v>
+        <v>267.9625093026149</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07948899269104004</v>
+        <v>0.2105028629302979</v>
       </c>
       <c r="J19" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="M19" t="n">
-        <v>712.0446297076888</v>
+        <v>724.8789978613926</v>
       </c>
       <c r="N19" t="n">
-        <v>1.694654941558838</v>
+        <v>1.257885932922363</v>
       </c>
       <c r="O19" t="n">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8717509542983831</v>
+        <v>0.8234943567213566</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6670678285761904</v>
+        <v>0.6303348419623364</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>118.2296538809034</v>
+        <v>114.9985662395674</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03623509407043457</v>
+        <v>0.04327702522277832</v>
       </c>
       <c r="E20" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>246.0265540005015</v>
+        <v>265.8118714699298</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1506760120391846</v>
+        <v>0.192345142364502</v>
       </c>
       <c r="J20" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K20" t="n">
         <v>7</v>
       </c>
       <c r="L20" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="M20" t="n">
-        <v>763.5605073801638</v>
+        <v>701.104417588284</v>
       </c>
       <c r="N20" t="n">
-        <v>2.127235889434814</v>
+        <v>1.602927207946777</v>
       </c>
       <c r="O20" t="n">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>641</v>
+        <v>665</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8451600721381484</v>
+        <v>0.8359751224572957</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6777903628821271</v>
+        <v>0.6208669282326146</v>
       </c>
     </row>
     <row r="21">
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>129.912556489156</v>
+        <v>116.1472322540053</v>
       </c>
       <c r="D21" t="n">
-        <v>0.08649969100952148</v>
+        <v>0.05478382110595703</v>
       </c>
       <c r="E21" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
         <v>7</v>
@@ -1704,40 +1704,40 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>225.6179388126253</v>
+        <v>263.2709423471169</v>
       </c>
       <c r="I21" t="n">
-        <v>0.296760082244873</v>
+        <v>0.2485699653625488</v>
       </c>
       <c r="J21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M21" t="n">
-        <v>728.8452453166706</v>
+        <v>757.4852380045951</v>
       </c>
       <c r="N21" t="n">
-        <v>1.46306300163269</v>
+        <v>1.360978126525879</v>
       </c>
       <c r="O21" t="n">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>701</v>
+        <v>739</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8217556369833883</v>
+        <v>0.8466673323430486</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6904446585027825</v>
+        <v>0.6524408277042623</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>92.11292564572135</v>
+        <v>89.40376645216817</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02979087829589844</v>
+        <v>0.06335115432739258</v>
       </c>
       <c r="E22" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>217.8565405806316</v>
+        <v>250.1311200252233</v>
       </c>
       <c r="I22" t="n">
-        <v>0.104485034942627</v>
+        <v>0.2218689918518066</v>
       </c>
       <c r="J22" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L22" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="M22" t="n">
-        <v>721.2608112214226</v>
+        <v>756.770282015847</v>
       </c>
       <c r="N22" t="n">
-        <v>1.189818859100342</v>
+        <v>1.372531890869141</v>
       </c>
       <c r="O22" t="n">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>671</v>
+        <v>726</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8722890191555919</v>
+        <v>0.8818614200678985</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6979503985365553</v>
+        <v>0.6694754987485285</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>96.59954141291166</v>
+        <v>101.8939242307399</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02639222145080566</v>
+        <v>0.04486489295959473</v>
       </c>
       <c r="E23" t="n">
         <v>33</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>170.657204182224</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1103000640869141</v>
+      </c>
+      <c r="J23" t="n">
+        <v>31</v>
+      </c>
+      <c r="K23" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>45</v>
+      </c>
+      <c r="M23" t="n">
+        <v>715.0184116267806</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.152017831802368</v>
+      </c>
+      <c r="O23" t="n">
+        <v>232</v>
+      </c>
+      <c r="P23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="n">
-        <v>249.5507623596364</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.07886075973510742</v>
-      </c>
-      <c r="J23" t="n">
-        <v>38</v>
-      </c>
-      <c r="K23" t="n">
-        <v>10</v>
-      </c>
-      <c r="L23" t="n">
-        <v>46</v>
-      </c>
-      <c r="M23" t="n">
-        <v>731.96334964789</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.830397844314575</v>
-      </c>
-      <c r="O23" t="n">
-        <v>243</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
       <c r="Q23" t="n">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8680268056325761</v>
+        <v>0.8574946846488679</v>
       </c>
       <c r="S23" t="n">
-        <v>0.659066587856233</v>
+        <v>0.7613247415630154</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>134.0668078327051</v>
+        <v>151.925388387101</v>
       </c>
       <c r="D24" t="n">
-        <v>0.05079817771911621</v>
+        <v>0.04810905456542969</v>
       </c>
       <c r="E24" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>251.5579597244762</v>
+        <v>250.2169156505441</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1930930614471436</v>
+        <v>0.1894729137420654</v>
       </c>
       <c r="J24" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="M24" t="n">
-        <v>682.6000430625619</v>
+        <v>734.4821839629788</v>
       </c>
       <c r="N24" t="n">
-        <v>1.324244022369385</v>
+        <v>1.441110134124756</v>
       </c>
       <c r="O24" t="n">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>680</v>
+        <v>739</v>
       </c>
       <c r="R24" t="n">
-        <v>0.803593906570531</v>
+        <v>0.7931530652420037</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6314709290145469</v>
+        <v>0.6593288154377396</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>84.9360435261807</v>
+        <v>135.528402863304</v>
       </c>
       <c r="D25" t="n">
-        <v>0.06611776351928711</v>
+        <v>0.05669903755187988</v>
       </c>
       <c r="E25" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>257.3426503539066</v>
+        <v>190.8734442218279</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2712688446044922</v>
+        <v>0.1588370800018311</v>
       </c>
       <c r="J25" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K25" t="n">
         <v>7</v>
       </c>
       <c r="L25" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M25" t="n">
-        <v>766.1336511566947</v>
+        <v>726.4237899815869</v>
       </c>
       <c r="N25" t="n">
-        <v>1.414407730102539</v>
+        <v>1.621381998062134</v>
       </c>
       <c r="O25" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>670</v>
+        <v>730</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8891367799887842</v>
+        <v>0.8134306657732956</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6641021446253205</v>
+        <v>0.7372423000812431</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>95.1897946860766</v>
+        <v>126.3074395540202</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02970695495605469</v>
+        <v>0.05399513244628906</v>
       </c>
       <c r="E26" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>180.7406171205637</v>
+        <v>225.7728764506411</v>
       </c>
       <c r="I26" t="n">
-        <v>0.06879496574401855</v>
+        <v>0.1884169578552246</v>
       </c>
       <c r="J26" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L26" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="M26" t="n">
-        <v>738.6730377641238</v>
+        <v>725.6356688901024</v>
       </c>
       <c r="N26" t="n">
-        <v>1.254360914230347</v>
+        <v>1.742033243179321</v>
       </c>
       <c r="O26" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>652</v>
+        <v>681</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8711340609179336</v>
+        <v>0.825935459116537</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7553171594462901</v>
+        <v>0.688861937015896</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>107.5810918757554</v>
+        <v>119.7711949721388</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0309760570526123</v>
+        <v>0.05751395225524902</v>
       </c>
       <c r="E27" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>235.787054177243</v>
+        <v>187.1114108581362</v>
       </c>
       <c r="I27" t="n">
-        <v>0.07804608345031738</v>
+        <v>0.1247720718383789</v>
       </c>
       <c r="J27" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M27" t="n">
-        <v>742.6421651278957</v>
+        <v>721.1511810191001</v>
       </c>
       <c r="N27" t="n">
-        <v>1.208980083465576</v>
+        <v>1.235074043273926</v>
       </c>
       <c r="O27" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>644</v>
+        <v>702</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8551373771549476</v>
+        <v>0.833916662518831</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6825024685520834</v>
+        <v>0.740537884727973</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>116.3739856142228</v>
+        <v>115.0383194585781</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02868795394897461</v>
+        <v>0.05306696891784668</v>
       </c>
       <c r="E28" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>260.3026120933318</v>
+        <v>235.6046116144477</v>
       </c>
       <c r="I28" t="n">
-        <v>0.08435893058776855</v>
+        <v>0.1427299976348877</v>
       </c>
       <c r="J28" t="n">
         <v>46</v>
       </c>
       <c r="K28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M28" t="n">
-        <v>709.5121652542294</v>
+        <v>737.9616143409297</v>
       </c>
       <c r="N28" t="n">
-        <v>1.489576101303101</v>
+        <v>1.290768146514893</v>
       </c>
       <c r="O28" t="n">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>636</v>
+        <v>700</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8359802815043712</v>
+        <v>0.8441134102058706</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6331245257788338</v>
+        <v>0.6807359528789785</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>121.1234046839671</v>
+        <v>80.99835010428855</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03216385841369629</v>
+        <v>0.05210709571838379</v>
       </c>
       <c r="E29" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>238.399412650148</v>
+        <v>243.865795475719</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1248600482940674</v>
+        <v>0.1794888973236084</v>
       </c>
       <c r="J29" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L29" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M29" t="n">
-        <v>721.5147182920159</v>
+        <v>686.8830745501701</v>
       </c>
       <c r="N29" t="n">
-        <v>1.570188999176025</v>
+        <v>1.262166976928711</v>
       </c>
       <c r="O29" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>610</v>
+        <v>644</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8321262177843123</v>
+        <v>0.8820784015426014</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6695848239735264</v>
+        <v>0.6449675286650159</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>77.88094866023873</v>
+        <v>128.0828716997299</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03898024559020996</v>
+        <v>0.03520488739013672</v>
       </c>
       <c r="E30" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>246.1190534299801</v>
+        <v>246.5267846148554</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1120550632476807</v>
+        <v>0.1595151424407959</v>
       </c>
       <c r="J30" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M30" t="n">
-        <v>729.5591792936031</v>
+        <v>712.8679477532169</v>
       </c>
       <c r="N30" t="n">
-        <v>1.228527069091797</v>
+        <v>1.533380031585693</v>
       </c>
       <c r="O30" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>672</v>
+        <v>625</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8932493060595207</v>
+        <v>0.8203273522067931</v>
       </c>
       <c r="S30" t="n">
-        <v>0.662646896351458</v>
+        <v>0.6541760849371238</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>82.54107511574742</v>
+        <v>113.0069643320811</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02977991104125977</v>
+        <v>0.06091094017028809</v>
       </c>
       <c r="E31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" t="n">
         <v>3</v>
       </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
       <c r="H31" t="n">
-        <v>235.0903888651515</v>
+        <v>259.5479534803093</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0833742618560791</v>
+        <v>0.1970422267913818</v>
       </c>
       <c r="J31" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L31" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M31" t="n">
-        <v>726.5980815371389</v>
+        <v>720.5902561461337</v>
       </c>
       <c r="N31" t="n">
-        <v>1.268554925918579</v>
+        <v>1.448066234588623</v>
       </c>
       <c r="O31" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="R31" t="n">
-        <v>0.8864006426480932</v>
+        <v>0.8431744484910665</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6764505786090007</v>
+        <v>0.6398120134618173</v>
       </c>
     </row>
   </sheetData>
